--- a/8月分_高速料金_車番別.xlsx
+++ b/8月分_高速料金_車番別.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;￥&quot;#,##0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="游ゴシック"/>
       <charset val="128"/>
@@ -55,12 +55,16 @@
     <font>
       <name val="游ゴシック"/>
       <b val="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="游ゴシック"/>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="2">
@@ -105,7 +109,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -122,15 +126,18 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -514,6 +521,7 @@
     <col width="11.625" customWidth="1" style="5" min="2" max="2"/>
     <col width="13" customWidth="1" style="5" min="3" max="3"/>
     <col width="9" customWidth="1" style="5" min="4" max="4"/>
+    <col width="34" customWidth="1" style="5" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="5">
@@ -522,9 +530,14 @@
           <t>8月分　高速料金</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>件数</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
@@ -548,7 +561,7 @@
           <t>山崎（正）</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="7" t="n">
         <v>140200</v>
       </c>
       <c r="D3" s="2" t="n">
@@ -565,7 +578,7 @@
           <t>石川</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="7" t="n">
         <v>101310</v>
       </c>
       <c r="D4" s="2" t="n">
@@ -582,7 +595,7 @@
           <t>関</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>212250</v>
       </c>
       <c r="D5" s="2" t="n">
@@ -599,7 +612,7 @@
           <t>仲林</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>339870</v>
       </c>
       <c r="D6" s="2" t="n">
@@ -616,7 +629,7 @@
           <t>山崎（文）</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>101330</v>
       </c>
       <c r="D7" s="2" t="n">
@@ -633,7 +646,7 @@
           <t>吉成</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <v>128880</v>
       </c>
       <c r="D8" s="2" t="n">
@@ -650,7 +663,7 @@
           <t>志賀</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <v>220240</v>
       </c>
       <c r="D9" s="2" t="n">
@@ -667,7 +680,7 @@
           <t>高橋</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="7" t="n">
         <v>178510</v>
       </c>
       <c r="D10" s="2" t="n">
@@ -684,7 +697,7 @@
           <t>横須賀</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="7" t="n">
         <v>341060</v>
       </c>
       <c r="D11" s="2" t="n">
@@ -701,7 +714,7 @@
           <t>海老澤</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="n">
         <v>238080</v>
       </c>
       <c r="D12" s="2" t="n">
@@ -718,7 +731,7 @@
           <t>根本</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="7" t="n">
         <v>79730</v>
       </c>
       <c r="D13" s="2" t="n">
@@ -735,7 +748,7 @@
           <t>砂押</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="7" t="n">
         <v>297380</v>
       </c>
       <c r="D14" s="2" t="n">
@@ -752,13 +765,17 @@
           <t>伊垣</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
-        <v>265900</v>
+      <c r="C15" s="7" t="n">
+        <v>286030</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="E15" s="2" t="n"/>
+        <v>87</v>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>車番46 の 8/20・8/21分 ￥20,130 を含む</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20.45" customFormat="1" customHeight="1" s="1">
       <c r="A16" s="1" t="n">
@@ -769,7 +786,7 @@
           <t>芳賀</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="7" t="n">
         <v>444500</v>
       </c>
       <c r="D16" s="2" t="n">
@@ -786,7 +803,7 @@
           <t>小林</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="7" t="n">
         <v>290840</v>
       </c>
       <c r="D17" s="2" t="n">
@@ -803,7 +820,7 @@
           <t>鶴田（伸）</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C18" s="7" t="n">
         <v>244450</v>
       </c>
       <c r="D18" s="2" t="n">
@@ -820,7 +837,7 @@
           <t>萩野間</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="9" t="n">
         <v>298970</v>
       </c>
       <c r="D19" s="3" t="n">
@@ -837,7 +854,7 @@
           <t>中川</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="3" t="n">
@@ -854,7 +871,7 @@
           <t>宇佐美</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="9" t="n">
         <v>184540</v>
       </c>
       <c r="D21" s="3" t="n">
@@ -871,7 +888,7 @@
           <t>安野</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="9" t="n">
         <v>8020</v>
       </c>
       <c r="D22" s="3" t="n">
@@ -888,7 +905,7 @@
           <t>神長</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="9" t="n">
         <v>12660</v>
       </c>
       <c r="D23" s="3" t="n">
@@ -905,7 +922,7 @@
           <t>関根</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="9" t="n">
         <v>66930</v>
       </c>
       <c r="D24" s="3" t="n">
@@ -922,7 +939,7 @@
           <t>小堀内</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C25" s="7" t="n">
         <v>76910</v>
       </c>
       <c r="D25" s="2" t="n">
@@ -939,13 +956,17 @@
           <t>木村</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n">
-        <v>79190</v>
+      <c r="C26" s="7" t="n">
+        <v>59060</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="E26" s="2" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>8/20・8/21分 ￥20,130 を車番9283 へ振替</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="20.45" customHeight="1" s="5">
       <c r="A27" s="1" t="n"/>
@@ -959,7 +980,7 @@
       <c r="A29" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D29" s="3" t="n">
@@ -971,7 +992,7 @@
       <c r="A30" s="1" t="n">
         <v>7777</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="9" t="n">
         <v>106250</v>
       </c>
       <c r="D30" s="3" t="n">
@@ -983,7 +1004,7 @@
       <c r="A31" s="1" t="n">
         <v>4444</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="3" t="n">
@@ -995,7 +1016,7 @@
       <c r="A32" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="9" t="n">
         <v>334190</v>
       </c>
       <c r="D32" s="3" t="n">
@@ -1007,7 +1028,7 @@
       <c r="A33" s="1" t="n">
         <v>999</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="9" t="n">
         <v>143680</v>
       </c>
       <c r="D33" s="3" t="n">
@@ -1019,7 +1040,7 @@
       <c r="A34" s="1" t="n">
         <v>3274</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="9" t="n">
         <v>1330</v>
       </c>
       <c r="D34" s="3" t="n">
@@ -1027,16 +1048,17 @@
       </c>
       <c r="E34" s="3" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36">
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C36" s="9" t="n">
+      <c r="C36" s="11" t="n">
         <v>4937200</v>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="10" t="n">
         <v>1416</v>
       </c>
     </row>

--- a/8月分_高速料金_車番別.xlsx
+++ b/8月分_高速料金_車番別.xlsx
@@ -561,8 +561,7 @@
   <cols>
     <col width="11.625" customWidth="1" style="5" min="2" max="2"/>
     <col width="13" customWidth="1" style="5" min="3" max="3"/>
-    <col width="9" customWidth="1" style="5" min="4" max="4"/>
-    <col width="34" customWidth="1" style="5" min="5" max="5"/>
+    <col width="34" customWidth="1" style="5" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="5">
@@ -573,11 +572,6 @@
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
-          <t>件数</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
           <t>備考</t>
         </is>
       </c>
@@ -605,9 +599,7 @@
       <c r="C3" s="7" t="n">
         <v>140200</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>45</v>
-      </c>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
     </row>
     <row r="4" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -622,9 +614,7 @@
       <c r="C4" s="7" t="n">
         <v>101310</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>29</v>
-      </c>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
     </row>
     <row r="5" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -639,9 +629,7 @@
       <c r="C5" s="7" t="n">
         <v>212250</v>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>62</v>
-      </c>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="n"/>
     </row>
     <row r="6" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -656,9 +644,7 @@
       <c r="C6" s="7" t="n">
         <v>339870</v>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>83</v>
-      </c>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
     </row>
     <row r="7" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -673,9 +659,7 @@
       <c r="C7" s="7" t="n">
         <v>101330</v>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>24</v>
-      </c>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
     </row>
     <row r="8" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -690,9 +674,7 @@
       <c r="C8" s="7" t="n">
         <v>128880</v>
       </c>
-      <c r="D8" s="2" t="n">
-        <v>46</v>
-      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="n"/>
     </row>
     <row r="9" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -707,9 +689,7 @@
       <c r="C9" s="7" t="n">
         <v>220240</v>
       </c>
-      <c r="D9" s="2" t="n">
-        <v>65</v>
-      </c>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
     </row>
     <row r="10" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -724,9 +704,7 @@
       <c r="C10" s="7" t="n">
         <v>178510</v>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>38</v>
-      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
     </row>
     <row r="11" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -741,9 +719,7 @@
       <c r="C11" s="7" t="n">
         <v>341060</v>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>94</v>
-      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
     </row>
     <row r="12" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -758,9 +734,7 @@
       <c r="C12" s="7" t="n">
         <v>238080</v>
       </c>
-      <c r="D12" s="2" t="n">
-        <v>78</v>
-      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
     </row>
     <row r="13" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -775,9 +749,7 @@
       <c r="C13" s="7" t="n">
         <v>79730</v>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="n"/>
     </row>
     <row r="14" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -792,9 +764,7 @@
       <c r="C14" s="7" t="n">
         <v>297380</v>
       </c>
-      <c r="D14" s="2" t="n">
-        <v>83</v>
-      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
     </row>
     <row r="15" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -809,14 +779,12 @@
       <c r="C15" s="7" t="n">
         <v>286030</v>
       </c>
-      <c r="D15" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>車番46 の 8/20・8/21分 ￥20,130 を含む</t>
         </is>
       </c>
+      <c r="E15" s="2" t="n"/>
     </row>
     <row r="16" ht="20.45" customFormat="1" customHeight="1" s="1">
       <c r="A16" s="1" t="n">
@@ -830,9 +798,7 @@
       <c r="C16" s="7" t="n">
         <v>444500</v>
       </c>
-      <c r="D16" s="2" t="n">
-        <v>115</v>
-      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
     </row>
     <row r="17" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -847,9 +813,7 @@
       <c r="C17" s="7" t="n">
         <v>290840</v>
       </c>
-      <c r="D17" s="2" t="n">
-        <v>87</v>
-      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="n"/>
     </row>
     <row r="18" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -864,9 +828,7 @@
       <c r="C18" s="7" t="n">
         <v>244450</v>
       </c>
-      <c r="D18" s="2" t="n">
-        <v>75</v>
-      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
     </row>
     <row r="19" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -881,9 +843,7 @@
       <c r="C19" s="9" t="n">
         <v>298970</v>
       </c>
-      <c r="D19" s="3" t="n">
-        <v>69</v>
-      </c>
+      <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
     </row>
     <row r="20" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -898,9 +858,7 @@
       <c r="C20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n"/>
     </row>
     <row r="21" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -915,9 +873,7 @@
       <c r="C21" s="9" t="n">
         <v>184540</v>
       </c>
-      <c r="D21" s="3" t="n">
-        <v>64</v>
-      </c>
+      <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
     </row>
     <row r="22" ht="20.45" customFormat="1" customHeight="1" s="1">
@@ -932,9 +888,7 @@
       <c r="C22" s="9" t="n">
         <v>8020</v>
       </c>
-      <c r="D22" s="3" t="n">
-        <v>7</v>
-      </c>
+      <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n"/>
     </row>
     <row r="23" ht="20.45" customHeight="1" s="5">
@@ -949,9 +903,7 @@
       <c r="C23" s="9" t="n">
         <v>12660</v>
       </c>
-      <c r="D23" s="3" t="n">
-        <v>14</v>
-      </c>
+      <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n"/>
     </row>
     <row r="24" ht="20.45" customHeight="1" s="5">
@@ -966,9 +918,7 @@
       <c r="C24" s="9" t="n">
         <v>66930</v>
       </c>
-      <c r="D24" s="3" t="n">
-        <v>28</v>
-      </c>
+      <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
     </row>
     <row r="25" ht="20.45" customHeight="1" s="5">
@@ -983,9 +933,7 @@
       <c r="C25" s="7" t="n">
         <v>76910</v>
       </c>
-      <c r="D25" s="2" t="n">
-        <v>34</v>
-      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="n"/>
     </row>
     <row r="26" ht="20.45" customHeight="1" s="5">
@@ -1000,14 +948,12 @@
       <c r="C26" s="7" t="n">
         <v>59060</v>
       </c>
-      <c r="D26" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>8/20・8/21分 ￥20,130 を車番9283 へ振替</t>
         </is>
       </c>
+      <c r="E26" s="2" t="n"/>
     </row>
     <row r="27" ht="20.45" customHeight="1" s="5">
       <c r="A27" s="1" t="n"/>
@@ -1024,9 +970,7 @@
       <c r="C29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="n"/>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="5">
@@ -1036,9 +980,7 @@
       <c r="C30" s="9" t="n">
         <v>106250</v>
       </c>
-      <c r="D30" s="3" t="n">
-        <v>30</v>
-      </c>
+      <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="n"/>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="5">
@@ -1048,9 +990,7 @@
       <c r="C31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="n"/>
     </row>
     <row r="32" ht="19.5" customHeight="1" s="5">
@@ -1060,9 +1000,7 @@
       <c r="C32" s="9" t="n">
         <v>334190</v>
       </c>
-      <c r="D32" s="3" t="n">
-        <v>88</v>
-      </c>
+      <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n"/>
     </row>
     <row r="33" ht="19.5" customHeight="1" s="5">
@@ -1072,9 +1010,7 @@
       <c r="C33" s="9" t="n">
         <v>143680</v>
       </c>
-      <c r="D33" s="3" t="n">
-        <v>34</v>
-      </c>
+      <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n"/>
     </row>
     <row r="34" ht="19.5" customHeight="1" s="5">
@@ -1084,9 +1020,7 @@
       <c r="C34" s="9" t="n">
         <v>1330</v>
       </c>
-      <c r="D34" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n"/>
     </row>
     <row r="35"/>
@@ -1098,9 +1032,6 @@
       </c>
       <c r="C36" s="11" t="n">
         <v>4937200</v>
-      </c>
-      <c r="D36" s="10" t="n">
-        <v>1416</v>
       </c>
     </row>
   </sheetData>
@@ -3010,11 +2941,7 @@
       <c r="I47" s="18" t="n">
         <v>140200</v>
       </c>
-      <c r="J47" s="16" t="inlineStr">
-        <is>
-          <t>45件</t>
-        </is>
-      </c>
+      <c r="J47" s="16" t="n"/>
       <c r="K47" s="16" t="n"/>
     </row>
     <row r="49">
@@ -4196,11 +4123,7 @@
       <c r="I78" s="18" t="n">
         <v>101310</v>
       </c>
-      <c r="J78" s="16" t="inlineStr">
-        <is>
-          <t>29件</t>
-        </is>
-      </c>
+      <c r="J78" s="16" t="n"/>
       <c r="K78" s="16" t="n"/>
     </row>
     <row r="80">
@@ -6681,11 +6604,7 @@
       <c r="I142" s="18" t="n">
         <v>212250</v>
       </c>
-      <c r="J142" s="16" t="inlineStr">
-        <is>
-          <t>62件</t>
-        </is>
-      </c>
+      <c r="J142" s="16" t="n"/>
       <c r="K142" s="16" t="n"/>
     </row>
     <row r="144">
@@ -10125,11 +10044,7 @@
       <c r="I227" s="18" t="n">
         <v>339870</v>
       </c>
-      <c r="J227" s="16" t="inlineStr">
-        <is>
-          <t>83件</t>
-        </is>
-      </c>
+      <c r="J227" s="16" t="n"/>
       <c r="K227" s="16" t="n"/>
     </row>
     <row r="229">
@@ -11104,11 +11019,7 @@
       <c r="I253" s="18" t="n">
         <v>101330</v>
       </c>
-      <c r="J253" s="16" t="inlineStr">
-        <is>
-          <t>24件</t>
-        </is>
-      </c>
+      <c r="J253" s="16" t="n"/>
       <c r="K253" s="16" t="n"/>
     </row>
     <row r="255">
@@ -12955,11 +12866,7 @@
       <c r="I301" s="18" t="n">
         <v>128880</v>
       </c>
-      <c r="J301" s="16" t="inlineStr">
-        <is>
-          <t>46件</t>
-        </is>
-      </c>
+      <c r="J301" s="16" t="n"/>
       <c r="K301" s="16" t="n"/>
     </row>
     <row r="303">
@@ -15573,11 +15480,7 @@
       <c r="I368" s="18" t="n">
         <v>220240</v>
       </c>
-      <c r="J368" s="16" t="inlineStr">
-        <is>
-          <t>65件</t>
-        </is>
-      </c>
+      <c r="J368" s="16" t="n"/>
       <c r="K368" s="16" t="n"/>
     </row>
     <row r="370">
@@ -17118,11 +17021,7 @@
       <c r="I408" s="18" t="n">
         <v>178510</v>
       </c>
-      <c r="J408" s="16" t="inlineStr">
-        <is>
-          <t>38件</t>
-        </is>
-      </c>
+      <c r="J408" s="16" t="n"/>
       <c r="K408" s="16" t="n"/>
     </row>
     <row r="410">
@@ -20867,11 +20766,7 @@
       <c r="I504" s="18" t="n">
         <v>341060</v>
       </c>
-      <c r="J504" s="16" t="inlineStr">
-        <is>
-          <t>94件</t>
-        </is>
-      </c>
+      <c r="J504" s="16" t="n"/>
       <c r="K504" s="16" t="n"/>
     </row>
     <row r="506">
@@ -24078,11 +23973,7 @@
       <c r="I584" s="18" t="n">
         <v>238080</v>
       </c>
-      <c r="J584" s="16" t="inlineStr">
-        <is>
-          <t>78件</t>
-        </is>
-      </c>
+      <c r="J584" s="16" t="n"/>
       <c r="K584" s="16" t="n"/>
     </row>
     <row r="586">
@@ -24850,11 +24741,7 @@
       <c r="I605" s="18" t="n">
         <v>79730</v>
       </c>
-      <c r="J605" s="16" t="inlineStr">
-        <is>
-          <t>19件</t>
-        </is>
-      </c>
+      <c r="J605" s="16" t="n"/>
       <c r="K605" s="16" t="n"/>
     </row>
     <row r="607">
@@ -28182,11 +28069,7 @@
       <c r="I690" s="18" t="n">
         <v>297380</v>
       </c>
-      <c r="J690" s="16" t="inlineStr">
-        <is>
-          <t>83件</t>
-        </is>
-      </c>
+      <c r="J690" s="16" t="n"/>
       <c r="K690" s="16" t="n"/>
     </row>
     <row r="692">
@@ -31740,11 +31623,7 @@
       <c r="I779" s="18" t="n">
         <v>286030</v>
       </c>
-      <c r="J779" s="16" t="inlineStr">
-        <is>
-          <t>87件</t>
-        </is>
-      </c>
+      <c r="J779" s="16" t="n"/>
       <c r="K779" s="16" t="n"/>
     </row>
     <row r="781">
@@ -36332,11 +36211,7 @@
       <c r="I896" s="18" t="n">
         <v>444500</v>
       </c>
-      <c r="J896" s="16" t="inlineStr">
-        <is>
-          <t>115件</t>
-        </is>
-      </c>
+      <c r="J896" s="16" t="n"/>
       <c r="K896" s="16" t="n"/>
     </row>
     <row r="898">
@@ -39830,11 +39705,7 @@
       <c r="I985" s="18" t="n">
         <v>290840</v>
       </c>
-      <c r="J985" s="16" t="inlineStr">
-        <is>
-          <t>87件</t>
-        </is>
-      </c>
+      <c r="J985" s="16" t="n"/>
       <c r="K985" s="16" t="n"/>
     </row>
     <row r="987">
@@ -42854,11 +42725,7 @@
       <c r="I1062" s="18" t="n">
         <v>244450</v>
       </c>
-      <c r="J1062" s="16" t="inlineStr">
-        <is>
-          <t>75件</t>
-        </is>
-      </c>
+      <c r="J1062" s="16" t="n"/>
       <c r="K1062" s="16" t="n"/>
     </row>
     <row r="1064">
@@ -45624,11 +45491,7 @@
       <c r="I1133" s="18" t="n">
         <v>298970</v>
       </c>
-      <c r="J1133" s="16" t="inlineStr">
-        <is>
-          <t>69件</t>
-        </is>
-      </c>
+      <c r="J1133" s="16" t="n"/>
       <c r="K1133" s="16" t="n"/>
     </row>
     <row r="1135">
@@ -48187,11 +48050,7 @@
       <c r="I1199" s="18" t="n">
         <v>184540</v>
       </c>
-      <c r="J1199" s="16" t="inlineStr">
-        <is>
-          <t>64件</t>
-        </is>
-      </c>
+      <c r="J1199" s="16" t="n"/>
       <c r="K1199" s="16" t="n"/>
     </row>
     <row r="1201">
@@ -48483,11 +48342,7 @@
       <c r="I1208" s="18" t="n">
         <v>8020</v>
       </c>
-      <c r="J1208" s="16" t="inlineStr">
-        <is>
-          <t>7件</t>
-        </is>
-      </c>
+      <c r="J1208" s="16" t="n"/>
       <c r="K1208" s="16" t="n"/>
     </row>
     <row r="1210">
@@ -49052,11 +48907,7 @@
       <c r="I1224" s="18" t="n">
         <v>12660</v>
       </c>
-      <c r="J1224" s="16" t="inlineStr">
-        <is>
-          <t>14件</t>
-        </is>
-      </c>
+      <c r="J1224" s="16" t="n"/>
       <c r="K1224" s="16" t="n"/>
     </row>
     <row r="1226">
@@ -50183,11 +50034,7 @@
       <c r="I1254" s="18" t="n">
         <v>66930</v>
       </c>
-      <c r="J1254" s="16" t="inlineStr">
-        <is>
-          <t>28件</t>
-        </is>
-      </c>
+      <c r="J1254" s="16" t="n"/>
       <c r="K1254" s="16" t="n"/>
     </row>
     <row r="1256">
@@ -51532,11 +51379,7 @@
       <c r="I1290" s="18" t="n">
         <v>76910</v>
       </c>
-      <c r="J1290" s="16" t="inlineStr">
-        <is>
-          <t>34件</t>
-        </is>
-      </c>
+      <c r="J1290" s="16" t="n"/>
       <c r="K1290" s="16" t="n"/>
     </row>
     <row r="1292">
@@ -52195,11 +52038,7 @@
       <c r="I1308" s="18" t="n">
         <v>59060</v>
       </c>
-      <c r="J1308" s="16" t="inlineStr">
-        <is>
-          <t>16件</t>
-        </is>
-      </c>
+      <c r="J1308" s="16" t="n"/>
       <c r="K1308" s="16" t="n"/>
     </row>
     <row r="1310">
@@ -53284,11 +53123,7 @@
       <c r="I1340" s="18" t="n">
         <v>106250</v>
       </c>
-      <c r="J1340" s="16" t="inlineStr">
-        <is>
-          <t>30件</t>
-        </is>
-      </c>
+      <c r="J1340" s="16" t="n"/>
       <c r="K1340" s="16" t="n"/>
     </row>
     <row r="1342">
@@ -56437,11 +56272,7 @@
       <c r="I1430" s="18" t="n">
         <v>334190</v>
       </c>
-      <c r="J1430" s="16" t="inlineStr">
-        <is>
-          <t>88件</t>
-        </is>
-      </c>
+      <c r="J1430" s="16" t="n"/>
       <c r="K1430" s="16" t="n"/>
     </row>
     <row r="1432">
@@ -57678,11 +57509,7 @@
       <c r="I1466" s="18" t="n">
         <v>143680</v>
       </c>
-      <c r="J1466" s="16" t="inlineStr">
-        <is>
-          <t>34件</t>
-        </is>
-      </c>
+      <c r="J1466" s="16" t="n"/>
       <c r="K1466" s="16" t="n"/>
     </row>
     <row r="1468">
@@ -57771,11 +57598,7 @@
       <c r="I1470" s="18" t="n">
         <v>1330</v>
       </c>
-      <c r="J1470" s="16" t="inlineStr">
-        <is>
-          <t>2件</t>
-        </is>
-      </c>
+      <c r="J1470" s="16" t="n"/>
       <c r="K1470" s="16" t="n"/>
     </row>
     <row r="1472">
@@ -57786,11 +57609,6 @@
       </c>
       <c r="I1472" s="20" t="n">
         <v>4937200</v>
-      </c>
-      <c r="J1472" s="6" t="inlineStr">
-        <is>
-          <t>1416件</t>
-        </is>
       </c>
     </row>
   </sheetData>
